--- a/templates/emission_factors_template.xlsx
+++ b/templates/emission_factors_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,11 +442,6 @@
           <t>unit</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>scope</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,12 +464,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>kgCO2e/L</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>scope_1</t>
+          <t>L</t>
         </is>
       </c>
     </row>
@@ -499,12 +489,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>kgCO2e/kWh</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>scope_2</t>
+          <t>kWh</t>
         </is>
       </c>
     </row>
@@ -529,12 +514,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>kgCO2e/passenger_km</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>scope_3</t>
+          <t>passenger_km</t>
         </is>
       </c>
     </row>
